--- a/APQP E ENTRADA DE COTAÇÕES 2026.xlsx
+++ b/APQP E ENTRADA DE COTAÇÕES 2026.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme\OneDrive\Desktop\gui\Programas\python\ExcelPython\Mehtal_v.1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1103AC5A-53AA-493C-9891-47F76F4ABEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F002406E-2CD3-4707-9F16-1C8D1E0FF87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FA53B8F-DE07-42FD-93F6-F3259E70693E}"/>
   </bookViews>
@@ -963,13 +963,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF8529"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -1012,6 +1005,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF8529"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1595,27 +1595,27 @@
         <v>22</v>
       </c>
       <c r="S2" s="11">
-        <f>SUBTOTAL(9,S4:S5)</f>
+        <f t="shared" ref="S2:X2" si="0">SUBTOTAL(9,S4:S5)</f>
         <v>2</v>
       </c>
       <c r="T2" s="11">
-        <f>SUBTOTAL(9,T4:T5)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="U2" s="12">
-        <f>SUBTOTAL(9,U4:U5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V2" s="11">
-        <f>SUBTOTAL(9,V4:V5)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="W2" s="11">
-        <f>SUBTOTAL(9,W4:W5)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X2" s="11">
-        <f>SUBTOTAL(9,X4:X5)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Y2" s="13"/>
@@ -2032,7 +2032,7 @@
         <v>95</v>
       </c>
       <c r="R5" s="41">
-        <f t="shared" ref="R5" si="0">P5*Q5*$R$2</f>
+        <f t="shared" ref="R5" si="1">P5*Q5*$R$2</f>
         <v>2253724</v>
       </c>
       <c r="S5" s="44">
@@ -2042,7 +2042,7 @@
         <v>3</v>
       </c>
       <c r="U5" s="44">
-        <f t="shared" ref="U5" si="1">S5-AI5-V5-W5-X5</f>
+        <f t="shared" ref="U5" si="2">S5-AI5-V5-W5-X5</f>
         <v>0</v>
       </c>
       <c r="V5" s="44">
@@ -2065,18 +2065,18 @@
         <v>46027</v>
       </c>
       <c r="AE5" s="42">
-        <f t="shared" ref="AE5" si="2">_xlfn.ISOWEEKNUM(AD5)</f>
+        <f t="shared" ref="AE5" si="3">_xlfn.ISOWEEKNUM(AD5)</f>
         <v>2</v>
       </c>
       <c r="AF5" s="46" t="s">
         <v>86</v>
       </c>
       <c r="AG5" s="43">
-        <f t="shared" ref="AG5" si="3">IF(AB5="",(AD5-AA5),(AD5-AB5))</f>
+        <f t="shared" ref="AG5" si="4">IF(AB5="",(AD5-AA5),(AD5-AB5))</f>
         <v>28</v>
       </c>
       <c r="AH5" s="51" t="str">
-        <f t="shared" ref="AH5" si="4">IF(W5=1,"CANCELADO",(IF(V5=0,(IF(AC5="",(IF(AB5="",(IF(AD5&lt;=AA5,"NO PRAZO","ATRASADO")),(IF(AD5&lt;=AB5,"NO PRAZO","ATRASADO")))),"PRAZO PERDIDO")),"DECLINADO")))</f>
+        <f t="shared" ref="AH5" si="5">IF(W5=1,"CANCELADO",(IF(V5=0,(IF(AC5="",(IF(AB5="",(IF(AD5&lt;=AA5,"NO PRAZO","ATRASADO")),(IF(AD5&lt;=AB5,"NO PRAZO","ATRASADO")))),"PRAZO PERDIDO")),"DECLINADO")))</f>
         <v>DECLINADO</v>
       </c>
       <c r="AI5" s="44"/>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="BA5" s="59">
-        <f t="shared" ref="BA5" si="5">AVERAGE(AM5:AZ5)</f>
+        <f t="shared" ref="BA5" si="6">AVERAGE(AM5:AZ5)</f>
         <v>0</v>
       </c>
       <c r="BB5" s="57" t="s">
@@ -2119,7 +2119,7 @@
       <c r="BE5" s="47"/>
       <c r="BF5" s="47"/>
       <c r="BG5" s="48">
-        <f t="shared" ref="BG5" si="6">P5*BE5</f>
+        <f t="shared" ref="BG5" si="7">P5*BE5</f>
         <v>0</v>
       </c>
       <c r="BH5" s="49">
@@ -2144,40 +2144,40 @@
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A4:BN5">
-    <cfRule type="expression" dxfId="8" priority="24">
-      <formula>$V4 = 1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:BN1 A2 C2:BN2 A3:BN3">
-    <cfRule type="expression" dxfId="7" priority="114">
+  <conditionalFormatting sqref="A1:BN1 A2 C2:BN2">
+    <cfRule type="expression" dxfId="8" priority="114">
       <formula>$V1 = 1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A3:BN5">
+    <cfRule type="expression" dxfId="7" priority="24">
+      <formula>$V3 = 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:J5">
+    <cfRule type="duplicateValues" dxfId="6" priority="248"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="N1:O5">
-    <cfRule type="cellIs" dxfId="6" priority="190" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="190" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH1:AH5">
-    <cfRule type="cellIs" dxfId="5" priority="195" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="195" operator="equal">
       <formula>"FALTA. INF. CLIENTE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="196" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="196" operator="equal">
       <formula>"PRAZO PERDIDO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="197" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="197" operator="equal">
       <formula>"DECLINADO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="198" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="198" operator="equal">
       <formula>"ATRASADO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="199" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="199" operator="equal">
       <formula>"NO PRAZO"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J5">
-    <cfRule type="duplicateValues" dxfId="0" priority="248"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2196,15 +2196,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009487DF3248FCD549B5D95C6664C039A6" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="e9ba9621effd660027664f83819bc50b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8fb20e23-5003-4e3a-b5f0-652bad7298ae" xmlns:ns3="3f6fd112-63a3-475d-82b8-980e7b6442a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0fdc9d632a45745dfd52666a86d29e22" ns2:_="" ns3:_="">
     <xsd:import namespace="8fb20e23-5003-4e3a-b5f0-652bad7298ae"/>
@@ -2433,6 +2424,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E886B802-92EF-480C-A9E1-2D8082D0E44E}">
   <ds:schemaRefs>
@@ -2445,14 +2445,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F9A967-6674-40D7-BF30-45FEC374CC78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{718C2E59-ABB4-41E8-9E4E-03881570C3C2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2469,4 +2461,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F9A967-6674-40D7-BF30-45FEC374CC78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/APQP E ENTRADA DE COTAÇÕES 2026.xlsx
+++ b/APQP E ENTRADA DE COTAÇÕES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme\OneDrive\Desktop\gui\Programas\python\ExcelPython\Mehtal_v.1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F002406E-2CD3-4707-9F16-1C8D1E0FF87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC77C68-ADA3-4B80-AC7B-317F99D3D105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FA53B8F-DE07-42FD-93F6-F3259E70693E}"/>
   </bookViews>
@@ -42,30 +42,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="98">
   <si>
     <t>ABERTURA DE COTAÇÃO 2026</t>
   </si>
@@ -271,12 +249,6 @@
     <t>Data Nomeação</t>
   </si>
   <si>
-    <t>Gustavo</t>
-  </si>
-  <si>
-    <t>recebemos o 3d SOMENTE NO DIA 17/03</t>
-  </si>
-  <si>
     <t>AGCO</t>
   </si>
   <si>
@@ -286,21 +258,6 @@
     <t>Novo</t>
   </si>
   <si>
-    <t>RFQ 21165</t>
-  </si>
-  <si>
-    <t>ACX4373020</t>
-  </si>
-  <si>
-    <t>2.12</t>
-  </si>
-  <si>
-    <t>Ved superior rad</t>
-  </si>
-  <si>
-    <t>Deivid Pereira</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
@@ -310,51 +267,6 @@
     <t>DECLINADO</t>
   </si>
   <si>
-    <t>Declinado</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>ABCDEFGH</t>
-  </si>
-  <si>
-    <t>N/OK</t>
-  </si>
-  <si>
-    <t>E-MAIL</t>
-  </si>
-  <si>
-    <t>Jair</t>
-  </si>
-  <si>
-    <t>VWCO</t>
-  </si>
-  <si>
-    <t>Resende - RJ</t>
-  </si>
-  <si>
-    <t>Protótipo</t>
-  </si>
-  <si>
-    <t>23G807125</t>
-  </si>
-  <si>
-    <t>05.11.25 (ZH99902-0152)</t>
-  </si>
-  <si>
-    <t>Conj. Suporte Da Escada</t>
-  </si>
-  <si>
-    <t>Renato Costa</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>6,026</t>
-  </si>
-  <si>
     <t xml:space="preserve">PN Methal   </t>
   </si>
   <si>
@@ -362,6 +274,69 @@
   </si>
   <si>
     <t xml:space="preserve"> Imagem </t>
+  </si>
+  <si>
+    <t>Guilherme</t>
+  </si>
+  <si>
+    <t>RFQ123</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Itens 1</t>
+  </si>
+  <si>
+    <t>Itens 2</t>
+  </si>
+  <si>
+    <t>Itens 3</t>
+  </si>
+  <si>
+    <t>Itens 4</t>
+  </si>
+  <si>
+    <t>Itens 5</t>
+  </si>
+  <si>
+    <t>Itens 6</t>
+  </si>
+  <si>
+    <t>Itens 7</t>
+  </si>
+  <si>
+    <t>Itens 8</t>
+  </si>
+  <si>
+    <t>Itens 9</t>
+  </si>
+  <si>
+    <t>1235</t>
+  </si>
+  <si>
+    <t>1236</t>
+  </si>
+  <si>
+    <t>1237</t>
+  </si>
+  <si>
+    <t>1238</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>1240</t>
+  </si>
+  <si>
+    <t>1241</t>
+  </si>
+  <si>
+    <t>1242</t>
   </si>
 </sst>
 </file>
@@ -648,7 +623,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -872,15 +847,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1045,70 +1012,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1429,12 +1332,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7485B9E-EE3C-492F-8B5F-CB0ABB6E1078}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BN12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="72" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" style="70" customWidth="1"/>
     <col min="2" max="2" width="10.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="66" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="64" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -1445,8 +1348,8 @@
     <col min="11" max="11" width="17.5703125" customWidth="1"/>
     <col min="12" max="12" width="23.85546875" customWidth="1"/>
     <col min="13" max="13" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="66" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" style="66" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="64" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" style="64" customWidth="1"/>
     <col min="16" max="16" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -1460,13 +1363,13 @@
     <col min="26" max="26" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="12" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.7109375" style="68" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.7109375" style="66" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="21" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="64" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="62" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -1490,8 +1393,8 @@
     <col min="56" max="56" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="17" style="71" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="11.5703125" style="71" customWidth="1"/>
+    <col min="59" max="59" width="17" style="69" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.5703125" style="69" customWidth="1"/>
     <col min="61" max="61" width="24.5703125" customWidth="1"/>
     <col min="62" max="64" width="15" customWidth="1"/>
     <col min="65" max="65" width="18" bestFit="1" customWidth="1"/>
@@ -1514,8 +1417,8 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
@@ -1529,54 +1432,54 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
-      <c r="AC1" s="67"/>
+      <c r="AC1" s="65"/>
       <c r="AD1" s="2"/>
       <c r="AE1" s="3"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="3"/>
       <c r="AH1" s="3"/>
-      <c r="AI1" s="75" t="s">
+      <c r="AI1" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="AJ1" s="75"/>
-      <c r="AK1" s="75"/>
-      <c r="AL1" s="75"/>
-      <c r="AM1" s="75"/>
-      <c r="AN1" s="75"/>
-      <c r="AO1" s="75"/>
-      <c r="AP1" s="75"/>
-      <c r="AQ1" s="75"/>
-      <c r="AR1" s="75"/>
-      <c r="AS1" s="75"/>
-      <c r="AT1" s="75"/>
-      <c r="AU1" s="75"/>
-      <c r="AV1" s="75"/>
-      <c r="AW1" s="75"/>
-      <c r="AX1" s="75"/>
-      <c r="AY1" s="75"/>
-      <c r="AZ1" s="75"/>
-      <c r="BA1" s="75"/>
-      <c r="BB1" s="75"/>
-      <c r="BC1" s="75"/>
-      <c r="BD1" s="75"/>
-      <c r="BE1" s="75"/>
-      <c r="BF1" s="75"/>
-      <c r="BG1" s="76" t="s">
+      <c r="AJ1" s="73"/>
+      <c r="AK1" s="73"/>
+      <c r="AL1" s="73"/>
+      <c r="AM1" s="73"/>
+      <c r="AN1" s="73"/>
+      <c r="AO1" s="73"/>
+      <c r="AP1" s="73"/>
+      <c r="AQ1" s="73"/>
+      <c r="AR1" s="73"/>
+      <c r="AS1" s="73"/>
+      <c r="AT1" s="73"/>
+      <c r="AU1" s="73"/>
+      <c r="AV1" s="73"/>
+      <c r="AW1" s="73"/>
+      <c r="AX1" s="73"/>
+      <c r="AY1" s="73"/>
+      <c r="AZ1" s="73"/>
+      <c r="BA1" s="73"/>
+      <c r="BB1" s="73"/>
+      <c r="BC1" s="73"/>
+      <c r="BD1" s="73"/>
+      <c r="BE1" s="73"/>
+      <c r="BF1" s="73"/>
+      <c r="BG1" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="BH1" s="76"/>
-      <c r="BI1" s="77"/>
-      <c r="BJ1" s="77"/>
-      <c r="BK1" s="77"/>
-      <c r="BL1" s="77"/>
-      <c r="BM1" s="77"/>
-      <c r="BN1" s="77"/>
+      <c r="BH1" s="74"/>
+      <c r="BI1" s="75"/>
+      <c r="BJ1" s="75"/>
+      <c r="BK1" s="75"/>
+      <c r="BL1" s="75"/>
+      <c r="BM1" s="75"/>
+      <c r="BN1" s="75"/>
     </row>
     <row r="2" spans="1:66" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="78"/>
+      <c r="B2" s="76"/>
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
@@ -1600,7 +1503,7 @@
       </c>
       <c r="T2" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U2" s="12">
         <f t="shared" si="0"/>
@@ -1616,7 +1519,7 @@
       </c>
       <c r="X2" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" s="13"/>
       <c r="Z2" s="13"/>
@@ -1639,11 +1542,11 @@
         <f>SUBTOTAL(9,BF4:BF5)</f>
         <v>0</v>
       </c>
-      <c r="BG2" s="69">
+      <c r="BG2" s="67">
         <f>SUBTOTAL(9,BG4:BG5)</f>
         <v>0</v>
       </c>
-      <c r="BH2" s="70">
+      <c r="BH2" s="68">
         <f>AVERAGE(BH4:BH5)</f>
         <v>0</v>
       </c>
@@ -1651,10 +1554,10 @@
     </row>
     <row r="3" spans="1:66" s="1" customFormat="1" ht="25.5">
       <c r="A3" s="19" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>5</v>
@@ -1662,8 +1565,8 @@
       <c r="D3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="73" t="s">
-        <v>98</v>
+      <c r="E3" s="71" t="s">
+        <v>76</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>7</v>
@@ -1851,46 +1754,40 @@
     </row>
     <row r="4" spans="1:66" s="1" customFormat="1">
       <c r="B4" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="G4" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="46">
-        <v>3</v>
-      </c>
-      <c r="E4" s="46" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F4" s="46" t="s">
+      <c r="H4" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="46" t="s">
-        <v>72</v>
-      </c>
       <c r="I4" s="46" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J4" s="54" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K4" s="54" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L4" s="54" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="M4" s="54" t="s">
         <v>77</v>
       </c>
       <c r="N4" s="54" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O4" s="54" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P4" s="55">
         <v>776</v>
@@ -1905,7 +1802,7 @@
         <v>1</v>
       </c>
       <c r="T4" s="56">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U4" s="44">
         <v>0</v>
@@ -1921,7 +1818,7 @@
       <c r="Z4" s="50">
         <v>46098</v>
       </c>
-      <c r="AA4" s="65">
+      <c r="AA4" s="63">
         <v>46069</v>
       </c>
       <c r="AB4" s="50">
@@ -1930,20 +1827,20 @@
       <c r="AC4" s="50">
         <v>46203</v>
       </c>
-      <c r="AD4" s="60">
+      <c r="AD4" s="59">
         <v>46246</v>
       </c>
       <c r="AE4" s="42">
         <v>33</v>
       </c>
       <c r="AF4" s="46" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AG4" s="43">
         <v>140</v>
       </c>
       <c r="AH4" s="51" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AI4" s="44"/>
       <c r="AJ4" s="52"/>
@@ -1962,7 +1859,7 @@
       <c r="AW4" s="57"/>
       <c r="AX4" s="57"/>
       <c r="AY4" s="57"/>
-      <c r="AZ4" s="62"/>
+      <c r="AZ4" s="60"/>
       <c r="BA4" s="58"/>
       <c r="BB4" s="57"/>
       <c r="BC4" s="57"/>
@@ -1986,107 +1883,100 @@
     </row>
     <row r="5" spans="1:66" s="1" customFormat="1">
       <c r="B5" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="46">
-        <v>0</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="C5" s="61"/>
+      <c r="D5" s="46"/>
       <c r="E5" s="46"/>
       <c r="F5" s="46" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="G5" s="46" t="s">
-        <v>88</v>
-      </c>
-      <c r="H5" s="61" t="s">
-        <v>89</v>
+        <v>69</v>
+      </c>
+      <c r="H5" s="46" t="s">
+        <v>70</v>
       </c>
       <c r="I5" s="46" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="J5" s="54" t="s">
         <v>90</v>
       </c>
       <c r="K5" s="54" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="L5" s="54" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M5" s="54" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="N5" s="54" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O5" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="P5" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q5" s="54" t="s">
-        <v>95</v>
+        <v>71</v>
+      </c>
+      <c r="P5" s="55">
+        <v>776</v>
+      </c>
+      <c r="Q5" s="45">
+        <v>5.0297999999999998</v>
       </c>
       <c r="R5" s="41">
-        <f t="shared" ref="R5" si="1">P5*Q5*$R$2</f>
-        <v>2253724</v>
+        <v>85869.745599999995</v>
       </c>
       <c r="S5" s="44">
         <v>1</v>
       </c>
       <c r="T5" s="56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" s="44">
-        <f t="shared" ref="U5" si="2">S5-AI5-V5-W5-X5</f>
         <v>0</v>
       </c>
       <c r="V5" s="44">
         <v>1</v>
       </c>
       <c r="W5" s="44"/>
-      <c r="X5" s="44"/>
+      <c r="X5" s="44">
+        <v>1</v>
+      </c>
       <c r="Y5" s="50">
-        <v>45988</v>
+        <v>46048</v>
       </c>
       <c r="Z5" s="50">
-        <v>46027</v>
-      </c>
-      <c r="AA5" s="65">
-        <v>45999</v>
-      </c>
-      <c r="AB5" s="50"/>
-      <c r="AC5" s="46"/>
-      <c r="AD5" s="60">
-        <v>46027</v>
+        <v>46098</v>
+      </c>
+      <c r="AA5" s="63">
+        <v>46069</v>
+      </c>
+      <c r="AB5" s="50">
+        <v>46106</v>
+      </c>
+      <c r="AC5" s="50">
+        <v>46203</v>
+      </c>
+      <c r="AD5" s="59">
+        <v>46246</v>
       </c>
       <c r="AE5" s="42">
-        <f t="shared" ref="AE5" si="3">_xlfn.ISOWEEKNUM(AD5)</f>
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AF5" s="46" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="AG5" s="43">
-        <f t="shared" ref="AG5" si="4">IF(AB5="",(AD5-AA5),(AD5-AB5))</f>
-        <v>28</v>
-      </c>
-      <c r="AH5" s="51" t="str">
-        <f t="shared" ref="AH5" si="5">IF(W5=1,"CANCELADO",(IF(V5=0,(IF(AC5="",(IF(AB5="",(IF(AD5&lt;=AA5,"NO PRAZO","ATRASADO")),(IF(AD5&lt;=AB5,"NO PRAZO","ATRASADO")))),"PRAZO PERDIDO")),"DECLINADO")))</f>
-        <v>DECLINADO</v>
+        <v>141</v>
+      </c>
+      <c r="AH5" s="51" t="s">
+        <v>73</v>
       </c>
       <c r="AI5" s="44"/>
       <c r="AJ5" s="52"/>
-      <c r="AK5" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL5" s="44" t="s">
-        <v>83</v>
-      </c>
+      <c r="AK5" s="44"/>
+      <c r="AL5" s="44"/>
       <c r="AM5" s="57"/>
       <c r="AN5" s="57"/>
       <c r="AO5" s="57"/>
@@ -2100,40 +1990,932 @@
       <c r="AW5" s="57"/>
       <c r="AX5" s="57"/>
       <c r="AY5" s="57"/>
-      <c r="AZ5" s="62">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="59">
-        <f t="shared" ref="BA5" si="6">AVERAGE(AM5:AZ5)</f>
-        <v>0</v>
-      </c>
-      <c r="BB5" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="BC5" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="BD5" s="57" t="s">
-        <v>84</v>
-      </c>
+      <c r="AZ5" s="60"/>
+      <c r="BA5" s="58"/>
+      <c r="BB5" s="57"/>
+      <c r="BC5" s="57"/>
+      <c r="BD5" s="57"/>
       <c r="BE5" s="47"/>
       <c r="BF5" s="47"/>
       <c r="BG5" s="48">
-        <f t="shared" ref="BG5" si="7">P5*BE5</f>
         <v>0</v>
       </c>
       <c r="BH5" s="49">
-        <f>BE5/Q5</f>
         <v>0</v>
       </c>
       <c r="BI5" s="53"/>
-      <c r="BJ5" s="44"/>
-      <c r="BK5" s="44"/>
-      <c r="BL5" s="44"/>
+      <c r="BJ5" s="50"/>
+      <c r="BK5" s="50"/>
+      <c r="BL5" s="50"/>
       <c r="BM5" s="44" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="BN5" s="44"/>
+    </row>
+    <row r="6" spans="1:66" s="1" customFormat="1">
+      <c r="B6" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="61"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="M6" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N6" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="O6" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" s="55">
+        <v>776</v>
+      </c>
+      <c r="Q6" s="45">
+        <v>5.0297999999999998</v>
+      </c>
+      <c r="R6" s="41">
+        <v>85870.745599999995</v>
+      </c>
+      <c r="S6" s="44">
+        <v>1</v>
+      </c>
+      <c r="T6" s="56">
+        <v>1</v>
+      </c>
+      <c r="U6" s="44">
+        <v>0</v>
+      </c>
+      <c r="V6" s="44"/>
+      <c r="W6" s="44"/>
+      <c r="X6" s="44">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="50">
+        <v>46048</v>
+      </c>
+      <c r="Z6" s="50">
+        <v>46098</v>
+      </c>
+      <c r="AA6" s="63">
+        <v>46069</v>
+      </c>
+      <c r="AB6" s="50">
+        <v>46106</v>
+      </c>
+      <c r="AC6" s="50">
+        <v>46203</v>
+      </c>
+      <c r="AD6" s="59">
+        <v>46246</v>
+      </c>
+      <c r="AE6" s="42">
+        <v>35</v>
+      </c>
+      <c r="AF6" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG6" s="43">
+        <v>142</v>
+      </c>
+      <c r="AH6" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI6" s="44"/>
+      <c r="AJ6" s="52"/>
+      <c r="AK6" s="44"/>
+      <c r="AL6" s="44"/>
+      <c r="AM6" s="57"/>
+      <c r="AN6" s="57"/>
+      <c r="AO6" s="57"/>
+      <c r="AP6" s="57"/>
+      <c r="AQ6" s="57"/>
+      <c r="AR6" s="57"/>
+      <c r="AS6" s="57"/>
+      <c r="AT6" s="57"/>
+      <c r="AU6" s="57"/>
+      <c r="AV6" s="57"/>
+      <c r="AW6" s="57"/>
+      <c r="AX6" s="57"/>
+      <c r="AY6" s="57"/>
+      <c r="AZ6" s="60"/>
+      <c r="BA6" s="58"/>
+      <c r="BB6" s="57"/>
+      <c r="BC6" s="57"/>
+      <c r="BD6" s="57"/>
+      <c r="BE6" s="47"/>
+      <c r="BF6" s="47"/>
+      <c r="BG6" s="48">
+        <v>0</v>
+      </c>
+      <c r="BH6" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI6" s="53"/>
+      <c r="BJ6" s="50"/>
+      <c r="BK6" s="50"/>
+      <c r="BL6" s="50"/>
+      <c r="BM6" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN6" s="44"/>
+    </row>
+    <row r="7" spans="1:66" s="1" customFormat="1">
+      <c r="B7" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="61"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="K7" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="M7" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="P7" s="55">
+        <v>776</v>
+      </c>
+      <c r="Q7" s="45">
+        <v>5.0297999999999998</v>
+      </c>
+      <c r="R7" s="41">
+        <v>85871.745599999995</v>
+      </c>
+      <c r="S7" s="44">
+        <v>1</v>
+      </c>
+      <c r="T7" s="56">
+        <v>1</v>
+      </c>
+      <c r="U7" s="44">
+        <v>0</v>
+      </c>
+      <c r="V7" s="44"/>
+      <c r="W7" s="44"/>
+      <c r="X7" s="44">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="50">
+        <v>46048</v>
+      </c>
+      <c r="Z7" s="50">
+        <v>46098</v>
+      </c>
+      <c r="AA7" s="63">
+        <v>46069</v>
+      </c>
+      <c r="AB7" s="50">
+        <v>46106</v>
+      </c>
+      <c r="AC7" s="50">
+        <v>46203</v>
+      </c>
+      <c r="AD7" s="59">
+        <v>46246</v>
+      </c>
+      <c r="AE7" s="42">
+        <v>36</v>
+      </c>
+      <c r="AF7" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG7" s="43">
+        <v>143</v>
+      </c>
+      <c r="AH7" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI7" s="44"/>
+      <c r="AJ7" s="52"/>
+      <c r="AK7" s="44"/>
+      <c r="AL7" s="44"/>
+      <c r="AM7" s="57"/>
+      <c r="AN7" s="57"/>
+      <c r="AO7" s="57"/>
+      <c r="AP7" s="57"/>
+      <c r="AQ7" s="57"/>
+      <c r="AR7" s="57"/>
+      <c r="AS7" s="57"/>
+      <c r="AT7" s="57"/>
+      <c r="AU7" s="57"/>
+      <c r="AV7" s="57"/>
+      <c r="AW7" s="57"/>
+      <c r="AX7" s="57"/>
+      <c r="AY7" s="57"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="58"/>
+      <c r="BB7" s="57"/>
+      <c r="BC7" s="57"/>
+      <c r="BD7" s="57"/>
+      <c r="BE7" s="47"/>
+      <c r="BF7" s="47"/>
+      <c r="BG7" s="48">
+        <v>0</v>
+      </c>
+      <c r="BH7" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="53"/>
+      <c r="BJ7" s="50"/>
+      <c r="BK7" s="50"/>
+      <c r="BL7" s="50"/>
+      <c r="BM7" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN7" s="44"/>
+    </row>
+    <row r="8" spans="1:66" s="1" customFormat="1">
+      <c r="B8" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="61"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="M8" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N8" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" s="55">
+        <v>776</v>
+      </c>
+      <c r="Q8" s="45">
+        <v>5.0297999999999998</v>
+      </c>
+      <c r="R8" s="41">
+        <v>85872.745599999995</v>
+      </c>
+      <c r="S8" s="44">
+        <v>1</v>
+      </c>
+      <c r="T8" s="56">
+        <v>1</v>
+      </c>
+      <c r="U8" s="44">
+        <v>0</v>
+      </c>
+      <c r="V8" s="44">
+        <v>1</v>
+      </c>
+      <c r="W8" s="44"/>
+      <c r="X8" s="44">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="50">
+        <v>46048</v>
+      </c>
+      <c r="Z8" s="50">
+        <v>46098</v>
+      </c>
+      <c r="AA8" s="63">
+        <v>46069</v>
+      </c>
+      <c r="AB8" s="50">
+        <v>46106</v>
+      </c>
+      <c r="AC8" s="50">
+        <v>46203</v>
+      </c>
+      <c r="AD8" s="59">
+        <v>46246</v>
+      </c>
+      <c r="AE8" s="42">
+        <v>37</v>
+      </c>
+      <c r="AF8" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG8" s="43">
+        <v>144</v>
+      </c>
+      <c r="AH8" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI8" s="44"/>
+      <c r="AJ8" s="52"/>
+      <c r="AK8" s="44"/>
+      <c r="AL8" s="44"/>
+      <c r="AM8" s="57"/>
+      <c r="AN8" s="57"/>
+      <c r="AO8" s="57"/>
+      <c r="AP8" s="57"/>
+      <c r="AQ8" s="57"/>
+      <c r="AR8" s="57"/>
+      <c r="AS8" s="57"/>
+      <c r="AT8" s="57"/>
+      <c r="AU8" s="57"/>
+      <c r="AV8" s="57"/>
+      <c r="AW8" s="57"/>
+      <c r="AX8" s="57"/>
+      <c r="AY8" s="57"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="58"/>
+      <c r="BB8" s="57"/>
+      <c r="BC8" s="57"/>
+      <c r="BD8" s="57"/>
+      <c r="BE8" s="47"/>
+      <c r="BF8" s="47"/>
+      <c r="BG8" s="48">
+        <v>0</v>
+      </c>
+      <c r="BH8" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI8" s="53"/>
+      <c r="BJ8" s="50"/>
+      <c r="BK8" s="50"/>
+      <c r="BL8" s="50"/>
+      <c r="BM8" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN8" s="44"/>
+    </row>
+    <row r="9" spans="1:66" s="1" customFormat="1">
+      <c r="B9" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="61"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="M9" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="O9" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="P9" s="55">
+        <v>776</v>
+      </c>
+      <c r="Q9" s="45">
+        <v>5.0297999999999998</v>
+      </c>
+      <c r="R9" s="41">
+        <v>85873.745599999995</v>
+      </c>
+      <c r="S9" s="44">
+        <v>1</v>
+      </c>
+      <c r="T9" s="56">
+        <v>1</v>
+      </c>
+      <c r="U9" s="44">
+        <v>0</v>
+      </c>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="50">
+        <v>46048</v>
+      </c>
+      <c r="Z9" s="50">
+        <v>46098</v>
+      </c>
+      <c r="AA9" s="63">
+        <v>46069</v>
+      </c>
+      <c r="AB9" s="50">
+        <v>46106</v>
+      </c>
+      <c r="AC9" s="50">
+        <v>46203</v>
+      </c>
+      <c r="AD9" s="59">
+        <v>46246</v>
+      </c>
+      <c r="AE9" s="42">
+        <v>38</v>
+      </c>
+      <c r="AF9" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG9" s="43">
+        <v>145</v>
+      </c>
+      <c r="AH9" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI9" s="44"/>
+      <c r="AJ9" s="52"/>
+      <c r="AK9" s="44"/>
+      <c r="AL9" s="44"/>
+      <c r="AM9" s="57"/>
+      <c r="AN9" s="57"/>
+      <c r="AO9" s="57"/>
+      <c r="AP9" s="57"/>
+      <c r="AQ9" s="57"/>
+      <c r="AR9" s="57"/>
+      <c r="AS9" s="57"/>
+      <c r="AT9" s="57"/>
+      <c r="AU9" s="57"/>
+      <c r="AV9" s="57"/>
+      <c r="AW9" s="57"/>
+      <c r="AX9" s="57"/>
+      <c r="AY9" s="57"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="58"/>
+      <c r="BB9" s="57"/>
+      <c r="BC9" s="57"/>
+      <c r="BD9" s="57"/>
+      <c r="BE9" s="47"/>
+      <c r="BF9" s="47"/>
+      <c r="BG9" s="48">
+        <v>0</v>
+      </c>
+      <c r="BH9" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="53"/>
+      <c r="BJ9" s="50"/>
+      <c r="BK9" s="50"/>
+      <c r="BL9" s="50"/>
+      <c r="BM9" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN9" s="44"/>
+    </row>
+    <row r="10" spans="1:66" s="1" customFormat="1">
+      <c r="B10" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="61"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="M10" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N10" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="O10" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="P10" s="55">
+        <v>776</v>
+      </c>
+      <c r="Q10" s="45">
+        <v>5.0297999999999998</v>
+      </c>
+      <c r="R10" s="41">
+        <v>85874.745599999995</v>
+      </c>
+      <c r="S10" s="44">
+        <v>1</v>
+      </c>
+      <c r="T10" s="56">
+        <v>1</v>
+      </c>
+      <c r="U10" s="44">
+        <v>0</v>
+      </c>
+      <c r="V10" s="44"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="44">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="50">
+        <v>46048</v>
+      </c>
+      <c r="Z10" s="50">
+        <v>46098</v>
+      </c>
+      <c r="AA10" s="63">
+        <v>46069</v>
+      </c>
+      <c r="AB10" s="50">
+        <v>46106</v>
+      </c>
+      <c r="AC10" s="50">
+        <v>46203</v>
+      </c>
+      <c r="AD10" s="59">
+        <v>46246</v>
+      </c>
+      <c r="AE10" s="42">
+        <v>39</v>
+      </c>
+      <c r="AF10" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG10" s="43">
+        <v>146</v>
+      </c>
+      <c r="AH10" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI10" s="44"/>
+      <c r="AJ10" s="52"/>
+      <c r="AK10" s="44"/>
+      <c r="AL10" s="44"/>
+      <c r="AM10" s="57"/>
+      <c r="AN10" s="57"/>
+      <c r="AO10" s="57"/>
+      <c r="AP10" s="57"/>
+      <c r="AQ10" s="57"/>
+      <c r="AR10" s="57"/>
+      <c r="AS10" s="57"/>
+      <c r="AT10" s="57"/>
+      <c r="AU10" s="57"/>
+      <c r="AV10" s="57"/>
+      <c r="AW10" s="57"/>
+      <c r="AX10" s="57"/>
+      <c r="AY10" s="57"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="58"/>
+      <c r="BB10" s="57"/>
+      <c r="BC10" s="57"/>
+      <c r="BD10" s="57"/>
+      <c r="BE10" s="47"/>
+      <c r="BF10" s="47"/>
+      <c r="BG10" s="48">
+        <v>0</v>
+      </c>
+      <c r="BH10" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="53"/>
+      <c r="BJ10" s="50"/>
+      <c r="BK10" s="50"/>
+      <c r="BL10" s="50"/>
+      <c r="BM10" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN10" s="44"/>
+    </row>
+    <row r="11" spans="1:66" s="1" customFormat="1">
+      <c r="B11" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="K11" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N11" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="P11" s="55">
+        <v>776</v>
+      </c>
+      <c r="Q11" s="45">
+        <v>5.0297999999999998</v>
+      </c>
+      <c r="R11" s="41">
+        <v>85875.745599999995</v>
+      </c>
+      <c r="S11" s="44">
+        <v>1</v>
+      </c>
+      <c r="T11" s="56">
+        <v>1</v>
+      </c>
+      <c r="U11" s="44">
+        <v>0</v>
+      </c>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="50">
+        <v>46048</v>
+      </c>
+      <c r="Z11" s="50">
+        <v>46098</v>
+      </c>
+      <c r="AA11" s="63">
+        <v>46069</v>
+      </c>
+      <c r="AB11" s="50">
+        <v>46106</v>
+      </c>
+      <c r="AC11" s="50">
+        <v>46203</v>
+      </c>
+      <c r="AD11" s="59">
+        <v>46246</v>
+      </c>
+      <c r="AE11" s="42">
+        <v>40</v>
+      </c>
+      <c r="AF11" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG11" s="43">
+        <v>147</v>
+      </c>
+      <c r="AH11" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI11" s="44"/>
+      <c r="AJ11" s="52"/>
+      <c r="AK11" s="44"/>
+      <c r="AL11" s="44"/>
+      <c r="AM11" s="57"/>
+      <c r="AN11" s="57"/>
+      <c r="AO11" s="57"/>
+      <c r="AP11" s="57"/>
+      <c r="AQ11" s="57"/>
+      <c r="AR11" s="57"/>
+      <c r="AS11" s="57"/>
+      <c r="AT11" s="57"/>
+      <c r="AU11" s="57"/>
+      <c r="AV11" s="57"/>
+      <c r="AW11" s="57"/>
+      <c r="AX11" s="57"/>
+      <c r="AY11" s="57"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="58"/>
+      <c r="BB11" s="57"/>
+      <c r="BC11" s="57"/>
+      <c r="BD11" s="57"/>
+      <c r="BE11" s="47"/>
+      <c r="BF11" s="47"/>
+      <c r="BG11" s="48">
+        <v>0</v>
+      </c>
+      <c r="BH11" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="53"/>
+      <c r="BJ11" s="50"/>
+      <c r="BK11" s="50"/>
+      <c r="BL11" s="50"/>
+      <c r="BM11" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN11" s="44"/>
+    </row>
+    <row r="12" spans="1:66" s="1" customFormat="1">
+      <c r="B12" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="61"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="K12" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="L12" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="M12" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N12" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="O12" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="55">
+        <v>776</v>
+      </c>
+      <c r="Q12" s="45">
+        <v>5.0297999999999998</v>
+      </c>
+      <c r="R12" s="41">
+        <v>85876.745599999995</v>
+      </c>
+      <c r="S12" s="44">
+        <v>1</v>
+      </c>
+      <c r="T12" s="56">
+        <v>1</v>
+      </c>
+      <c r="U12" s="44">
+        <v>0</v>
+      </c>
+      <c r="V12" s="44"/>
+      <c r="W12" s="44"/>
+      <c r="X12" s="44">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="50">
+        <v>46048</v>
+      </c>
+      <c r="Z12" s="50">
+        <v>46098</v>
+      </c>
+      <c r="AA12" s="63">
+        <v>46069</v>
+      </c>
+      <c r="AB12" s="50">
+        <v>46106</v>
+      </c>
+      <c r="AC12" s="50">
+        <v>46203</v>
+      </c>
+      <c r="AD12" s="59">
+        <v>46246</v>
+      </c>
+      <c r="AE12" s="42">
+        <v>41</v>
+      </c>
+      <c r="AF12" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG12" s="43">
+        <v>148</v>
+      </c>
+      <c r="AH12" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI12" s="44"/>
+      <c r="AJ12" s="52"/>
+      <c r="AK12" s="44"/>
+      <c r="AL12" s="44"/>
+      <c r="AM12" s="57"/>
+      <c r="AN12" s="57"/>
+      <c r="AO12" s="57"/>
+      <c r="AP12" s="57"/>
+      <c r="AQ12" s="57"/>
+      <c r="AR12" s="57"/>
+      <c r="AS12" s="57"/>
+      <c r="AT12" s="57"/>
+      <c r="AU12" s="57"/>
+      <c r="AV12" s="57"/>
+      <c r="AW12" s="57"/>
+      <c r="AX12" s="57"/>
+      <c r="AY12" s="57"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="58"/>
+      <c r="BB12" s="57"/>
+      <c r="BC12" s="57"/>
+      <c r="BD12" s="57"/>
+      <c r="BE12" s="47"/>
+      <c r="BF12" s="47"/>
+      <c r="BG12" s="48">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="49">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="53"/>
+      <c r="BJ12" s="50"/>
+      <c r="BK12" s="50"/>
+      <c r="BL12" s="50"/>
+      <c r="BM12" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN12" s="44"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -2149,20 +2931,20 @@
       <formula>$V1 = 1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:BN5">
+  <conditionalFormatting sqref="A3:BN12">
     <cfRule type="expression" dxfId="7" priority="24">
       <formula>$V3 = 1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J5">
+  <conditionalFormatting sqref="J1:J12">
     <cfRule type="duplicateValues" dxfId="6" priority="248"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:O5">
+  <conditionalFormatting sqref="N1:O12">
     <cfRule type="cellIs" dxfId="5" priority="190" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH1:AH5">
+  <conditionalFormatting sqref="AH1:AH12">
     <cfRule type="cellIs" dxfId="4" priority="195" operator="equal">
       <formula>"FALTA. INF. CLIENTE"</formula>
     </cfRule>
@@ -2196,6 +2978,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009487DF3248FCD549B5D95C6664C039A6" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="e9ba9621effd660027664f83819bc50b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8fb20e23-5003-4e3a-b5f0-652bad7298ae" xmlns:ns3="3f6fd112-63a3-475d-82b8-980e7b6442a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0fdc9d632a45745dfd52666a86d29e22" ns2:_="" ns3:_="">
     <xsd:import namespace="8fb20e23-5003-4e3a-b5f0-652bad7298ae"/>
@@ -2424,15 +3215,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E886B802-92EF-480C-A9E1-2D8082D0E44E}">
   <ds:schemaRefs>
@@ -2445,6 +3227,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F9A967-6674-40D7-BF30-45FEC374CC78}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{718C2E59-ABB4-41E8-9E4E-03881570C3C2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2461,12 +3251,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F9A967-6674-40D7-BF30-45FEC374CC78}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>